--- a/bd/usuarios.xlsx
+++ b/bd/usuarios.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,36 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id_usuario</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>nombre</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>password_hash</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>rol</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>fecha_registro</t>
         </is>
@@ -547,6 +535,36 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-02-06 16:40:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tatiana</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>tr3303419@gmail.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:04:49</t>
         </is>
       </c>
     </row>

--- a/bd/usuarios.xlsx
+++ b/bd/usuarios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,126 +445,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>fecha_registro</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Nico</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>nico@gmail.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-02-06 14:55:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Julio</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>julio@gmail.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-02-06 14:55:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Alvaréx Freo</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>alv@gmail.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-02-06 16:40:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>tatiana</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>tr3303419@gmail.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-02-22 23:04:49</t>
         </is>
       </c>
     </row>

--- a/bd/usuarios.xlsx
+++ b/bd/usuarios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,6 +445,126 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>fecha_registro</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nico</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>nico@gmail.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-02-06 14:55:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Julio</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>julio@gmail.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-02-06 14:55:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Alvaréx Freo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>alv@gmail.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-02-06 16:40:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tatiana</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>tr3303419@gmail.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:04:49</t>
         </is>
       </c>
     </row>

--- a/bd/usuarios.xlsx
+++ b/bd/usuarios.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,36 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id_usuario</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>nombre</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>password_hash</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>rol</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>fecha_registro</t>
         </is>
@@ -547,6 +535,66 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-02-06 16:40:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>jilmer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>hola@gmail.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-02-20 15:47:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>hola2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-02-20 15:47:36</t>
         </is>
       </c>
     </row>

--- a/bd/usuarios.xlsx
+++ b/bd/usuarios.xlsx
@@ -579,12 +579,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hola2@gmail.com</t>
+          <t>hola3@gmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>123456789</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">

--- a/bd/usuarios.xlsx
+++ b/bd/usuarios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,6 +595,36 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-02-20 15:47:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>tatiana</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>tr3303419@gmail.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:46:04</t>
         </is>
       </c>
     </row>

--- a/bd/usuarios.xlsx
+++ b/bd/usuarios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,6 +595,36 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-02-20 15:47:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tatiana Rivera</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>tatis@gmail.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-02-25 22:35:53</t>
         </is>
       </c>
     </row>

--- a/bd/usuarios.xlsx
+++ b/bd/usuarios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,17 +544,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>tatiana</t>
+          <t>jilmer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>tr3303419@gmail.com</t>
+          <t>hola@gmail.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>123456</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -564,7 +564,37 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-22 23:04:49</t>
+          <t>2026-02-20 15:47:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>hola3@gmail.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-02-20 15:47:36</t>
         </is>
       </c>
     </row>

--- a/bd/usuarios.xlsx
+++ b/bd/usuarios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,6 +628,36 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tatiana Rivera</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>tr3303419@gmail.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:54:23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bd/usuarios.xlsx
+++ b/bd/usuarios.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>123456</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">

--- a/bd/usuarios.xlsx
+++ b/bd/usuarios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>estado</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>fecha_registro</t>
         </is>
       </c>
@@ -474,6 +479,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>2026-02-06 14:55:32</t>
         </is>
       </c>
@@ -504,6 +514,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>2026-02-06 14:55:32</t>
         </is>
       </c>
@@ -534,6 +549,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>2026-02-06 16:40:07</t>
         </is>
       </c>
@@ -564,6 +584,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>2026-02-20 15:47:06</t>
         </is>
       </c>
@@ -594,6 +619,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>2026-02-20 15:47:36</t>
         </is>
       </c>
@@ -624,6 +654,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>2026-02-25 22:35:53</t>
         </is>
       </c>
@@ -653,6 +688,11 @@
         </is>
       </c>
       <c r="F8" t="inlineStr">
+        <is>
+          <t>inactivo</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>2026-02-26 22:54:23</t>
         </is>

--- a/bd/usuarios.xlsx
+++ b/bd/usuarios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,21 @@
           <t>fecha_registro</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>email_verified</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>verification_code</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>verification_code_expiry</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -487,6 +502,11 @@
           <t>2026-02-06 14:55:32</t>
         </is>
       </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -522,6 +542,11 @@
           <t>2026-02-06 14:55:32</t>
         </is>
       </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -557,6 +582,11 @@
           <t>2026-02-06 16:40:07</t>
         </is>
       </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -592,6 +622,11 @@
           <t>2026-02-20 15:47:06</t>
         </is>
       </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -627,6 +662,11 @@
           <t>2026-02-20 15:47:36</t>
         </is>
       </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -662,6 +702,11 @@
           <t>2026-02-25 22:35:53</t>
         </is>
       </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -695,6 +740,99 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>2026-02-26 22:54:23</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>david@gmail.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4321</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:37:39</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>rodriguezsierradavidsantiago@gmail.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>54321</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-03-04 22:56:35</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>844313</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-03-04 23:45:18</t>
         </is>
       </c>
     </row>

--- a/bd/usuarios.xlsx
+++ b/bd/usuarios.xlsx
@@ -545,8 +545,16 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>801703</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-03-06 14:07:29</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
